--- a/human_resources_forms/011_workplace_incident_investigation_request_form--human_resources_forms.xlsx
+++ b/human_resources_forms/011_workplace_incident_investigation_request_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'on_hold'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'On Hold'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'review_and_update'}</t>
+          <t>review_and_update</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Review and Update'}</t>
+          <t>Review and Update</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'close_and_review'}</t>
+          <t>close_and_review</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Close and Review'}</t>
+          <t>Close and Review</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'close'}</t>
+          <t>close</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Close'}</t>
+          <t>Close</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'escalate'}</t>
+          <t>escalate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Escalate'}</t>
+          <t>Escalate</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'follow_up'}</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Follow Up'}</t>
+          <t>Follow Up</t>
         </is>
       </c>
     </row>
